--- a/research/traditional_assets/database/data/morocco/morocco_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_financial_svcs_non_bank_insurance.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.006650000000000003</v>
+        <v>-0.002399999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.335</v>
+        <v>-0.07304999999999999</v>
       </c>
       <c r="G2">
-        <v>0.0005966850828729281</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4.91</v>
+        <v>12.64</v>
       </c>
       <c r="L2">
-        <v>0.01808471454880295</v>
+        <v>0.02853273137697517</v>
       </c>
       <c r="M2">
-        <v>30.391</v>
+        <v>19.8252</v>
       </c>
       <c r="N2">
-        <v>0.06384663865546218</v>
+        <v>0.07506702006815601</v>
       </c>
       <c r="O2">
-        <v>6.189613034623218</v>
+        <v>1.568449367088608</v>
       </c>
       <c r="P2">
-        <v>30.391</v>
+        <v>19.8252</v>
       </c>
       <c r="Q2">
-        <v>0.06384663865546218</v>
+        <v>0.07506702006815601</v>
       </c>
       <c r="R2">
-        <v>6.189613034623218</v>
+        <v>1.568449367088608</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.07200000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="V2">
-        <v>0.0001512605042016807</v>
+        <v>2.271866717152594e-05</v>
       </c>
       <c r="W2">
-        <v>0.01756768760544276</v>
+        <v>0.06396469083191074</v>
       </c>
       <c r="X2">
-        <v>0.04274558144940648</v>
+        <v>0.1226267407833072</v>
       </c>
       <c r="Y2">
-        <v>-0.02517789384396371</v>
+        <v>-0.0586620499513965</v>
       </c>
       <c r="Z2">
-        <v>0.2627918659383993</v>
+        <v>0.3227230540819731</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0346824352785145</v>
+        <v>0.06567231131365076</v>
       </c>
       <c r="AC2">
-        <v>-0.0346824352785145</v>
+        <v>-0.06567231131365076</v>
       </c>
       <c r="AD2">
-        <v>828.5999999999999</v>
+        <v>1215.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>828.5999999999999</v>
+        <v>1215.3</v>
       </c>
       <c r="AG2">
-        <v>828.5279999999999</v>
+        <v>1215.294</v>
       </c>
       <c r="AH2">
-        <v>0.6351372068066841</v>
+        <v>0.8214816817628769</v>
       </c>
       <c r="AI2">
-        <v>0.7521103748751929</v>
+        <v>0.8672661100406766</v>
       </c>
       <c r="AJ2">
-        <v>0.6351170691621798</v>
+        <v>0.8214809577435084</v>
       </c>
       <c r="AK2">
-        <v>0.7520941733507136</v>
+        <v>0.8672655417064513</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.05860000000000001</v>
+        <v>-0.029</v>
       </c>
       <c r="E3">
-        <v>-0.415</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.03</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L3">
-        <v>0.01479885057471265</v>
+        <v>0.123314606741573</v>
       </c>
       <c r="M3">
-        <v>18.2</v>
+        <v>16.1</v>
       </c>
       <c r="N3">
-        <v>0.07923378319547236</v>
+        <v>0.09448356807511737</v>
       </c>
       <c r="O3">
-        <v>17.66990291262136</v>
+        <v>1.83371298405467</v>
       </c>
       <c r="P3">
-        <v>18.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q3">
-        <v>0.07923378319547236</v>
+        <v>0.09448356807511737</v>
       </c>
       <c r="R3">
-        <v>17.66990291262136</v>
+        <v>1.83371298405467</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,52 +761,52 @@
         <v>0.006</v>
       </c>
       <c r="V3">
-        <v>2.61210274270788e-05</v>
+        <v>3.52112676056338e-05</v>
       </c>
       <c r="W3">
-        <v>0.01053169734151329</v>
+        <v>0.08788788788788787</v>
       </c>
       <c r="X3">
-        <v>0.03503158948501178</v>
+        <v>0.0662324366777982</v>
       </c>
       <c r="Y3">
-        <v>-0.02449989214349848</v>
+        <v>0.02165545121008967</v>
       </c>
       <c r="Z3">
-        <v>0.2529124908246546</v>
+        <v>0.2453531086101021</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03310531255093351</v>
+        <v>0.05996605274369608</v>
       </c>
       <c r="AC3">
-        <v>-0.03310531255093351</v>
+        <v>-0.05996605274369608</v>
       </c>
       <c r="AD3">
-        <v>190.3</v>
+        <v>172.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>190.3</v>
+        <v>172.4</v>
       </c>
       <c r="AG3">
-        <v>190.294</v>
+        <v>172.394</v>
       </c>
       <c r="AH3">
-        <v>0.4530952380952381</v>
+        <v>0.5029171528588098</v>
       </c>
       <c r="AI3">
-        <v>0.6557546519641626</v>
+        <v>0.6800788954635109</v>
       </c>
       <c r="AJ3">
-        <v>0.4530874250584532</v>
+        <v>0.5029084523066332</v>
       </c>
       <c r="AK3">
-        <v>0.6557475344080167</v>
+        <v>0.6800713231871366</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Societe d'Equipement Domestique et Menager (EQDOM) S.A (CBSE:EQD)</t>
+          <t>Maroc Leasing S.A. (CBSE:MLE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0453</v>
+        <v>0.0242</v>
       </c>
       <c r="E4">
-        <v>-0.255</v>
+        <v>-0.0574</v>
       </c>
       <c r="G4">
-        <v>0.0008023774145616642</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="L4">
-        <v>0.0192174343734522</v>
+        <v>0.01038192576654115</v>
       </c>
       <c r="M4">
-        <v>12.191</v>
+        <v>3.7252</v>
       </c>
       <c r="N4">
-        <v>0.04949654892407632</v>
+        <v>0.03975667022411953</v>
       </c>
       <c r="O4">
-        <v>3.14201030927835</v>
+        <v>0.9650777202072539</v>
       </c>
       <c r="P4">
-        <v>12.191</v>
+        <v>3.7252</v>
       </c>
       <c r="Q4">
-        <v>0.04949654892407632</v>
+        <v>0.03975667022411953</v>
       </c>
       <c r="R4">
-        <v>3.14201030927835</v>
+        <v>0.9650777202072539</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.0002679658952496955</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.02460367786937223</v>
+        <v>0.04004149377593361</v>
       </c>
       <c r="X4">
-        <v>0.05045957341380118</v>
+        <v>0.1790210448888163</v>
       </c>
       <c r="Y4">
-        <v>-0.02585589554442895</v>
+        <v>-0.1389795511128827</v>
       </c>
       <c r="Z4">
-        <v>0.2663788701788921</v>
+        <v>0.3434642032332564</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0362595580060955</v>
+        <v>0.07137856988360544</v>
       </c>
       <c r="AC4">
-        <v>-0.0362595580060955</v>
+        <v>-0.07137856988360544</v>
       </c>
       <c r="AD4">
-        <v>638.3</v>
+        <v>1042.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>638.3</v>
+        <v>1042.9</v>
       </c>
       <c r="AG4">
-        <v>638.2339999999999</v>
+        <v>1042.9</v>
       </c>
       <c r="AH4">
-        <v>0.7215690707664482</v>
+        <v>0.9175611472813654</v>
       </c>
       <c r="AI4">
-        <v>0.7865680837954405</v>
+        <v>0.9086077713887436</v>
       </c>
       <c r="AJ4">
-        <v>0.721548295486663</v>
+        <v>0.9175611472813654</v>
       </c>
       <c r="AK4">
-        <v>0.7865507237803691</v>
+        <v>0.9086077713887436</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/morocco/morocco_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.002399999999999999</v>
+        <v>0.0264</v>
       </c>
       <c r="E2">
-        <v>-0.07304999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.05920550038197098</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.03418640183346066</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.03093964858670742</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01979277224244074</v>
       </c>
       <c r="K2">
-        <v>12.64</v>
+        <v>26.12</v>
       </c>
       <c r="L2">
-        <v>0.02853273137697517</v>
+        <v>0.04988540870893813</v>
       </c>
       <c r="M2">
-        <v>19.8252</v>
+        <v>8.3188</v>
       </c>
       <c r="N2">
-        <v>0.07506702006815601</v>
+        <v>0.01135362358400437</v>
       </c>
       <c r="O2">
-        <v>1.568449367088608</v>
+        <v>0.3184839203675344</v>
       </c>
       <c r="P2">
-        <v>19.8252</v>
+        <v>8.3188</v>
       </c>
       <c r="Q2">
-        <v>0.07506702006815601</v>
+        <v>0.01135362358400437</v>
       </c>
       <c r="R2">
-        <v>1.568449367088608</v>
+        <v>0.3184839203675344</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.006</v>
+        <v>18.509</v>
       </c>
       <c r="V2">
-        <v>2.271866717152594e-05</v>
+        <v>0.02526136208543742</v>
       </c>
       <c r="W2">
-        <v>0.06396469083191074</v>
+        <v>0.09617755856966709</v>
       </c>
       <c r="X2">
-        <v>0.1226267407833072</v>
+        <v>0.0729643085293651</v>
       </c>
       <c r="Y2">
-        <v>-0.0586620499513965</v>
+        <v>0.02321325004030199</v>
       </c>
       <c r="Z2">
-        <v>0.3227230540819731</v>
+        <v>0.3637667224312621</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06567231131365076</v>
+        <v>0.06067503148531356</v>
       </c>
       <c r="AC2">
-        <v>-0.06567231131365076</v>
+        <v>-0.06067503148531356</v>
       </c>
       <c r="AD2">
-        <v>1215.3</v>
+        <v>1200.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1215.3</v>
+        <v>1200.9</v>
       </c>
       <c r="AG2">
-        <v>1215.294</v>
+        <v>1182.391</v>
       </c>
       <c r="AH2">
-        <v>0.8214816817628769</v>
+        <v>0.6210695076541167</v>
       </c>
       <c r="AI2">
-        <v>0.8672661100406766</v>
+        <v>0.8268383365464059</v>
       </c>
       <c r="AJ2">
-        <v>0.8214809577435084</v>
+        <v>0.6174072145918914</v>
       </c>
       <c r="AK2">
-        <v>0.8672655417064513</v>
+        <v>0.8246031253421634</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="AN2">
+        <v>60.65151515151516</v>
+      </c>
+      <c r="AO2">
+        <v>3.785046728971962</v>
+      </c>
+      <c r="AP2">
+        <v>59.71671717171717</v>
+      </c>
+      <c r="AQ2">
+        <v>3.785046728971962</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salafin S.A. (CBSE:SLF)</t>
+          <t>Hightech Payment Systems S.A. (CBSE:HPS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.029</v>
+        <v>0.144</v>
       </c>
       <c r="E3">
-        <v>-0.08869999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2693310165073849</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.155516941789748</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1407471763683753</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1005186923765188</v>
       </c>
       <c r="K3">
-        <v>8.779999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="L3">
-        <v>0.123314606741573</v>
+        <v>0.08323197219808863</v>
       </c>
       <c r="M3">
-        <v>16.1</v>
+        <v>3.91</v>
       </c>
       <c r="N3">
-        <v>0.09448356807511737</v>
+        <v>0.00837617823479006</v>
       </c>
       <c r="O3">
-        <v>1.83371298405467</v>
+        <v>0.4081419624217119</v>
       </c>
       <c r="P3">
-        <v>16.1</v>
+        <v>3.91</v>
       </c>
       <c r="Q3">
-        <v>0.09448356807511737</v>
+        <v>0.00837617823479006</v>
       </c>
       <c r="R3">
-        <v>1.83371298405467</v>
+        <v>0.4081419624217119</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.006</v>
+        <v>18.5</v>
       </c>
       <c r="V3">
-        <v>3.52112676056338e-05</v>
+        <v>0.03963153384747215</v>
       </c>
       <c r="W3">
-        <v>0.08788788788788787</v>
+        <v>0.1626485568760611</v>
       </c>
       <c r="X3">
-        <v>0.0662324366777982</v>
+        <v>0.05897808526526414</v>
       </c>
       <c r="Y3">
-        <v>0.02165545121008967</v>
+        <v>0.103670471610797</v>
       </c>
       <c r="Z3">
-        <v>0.2453531086101021</v>
+        <v>3.021790496193227</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.3037464293131351</v>
       </c>
       <c r="AB3">
-        <v>0.05996605274369608</v>
+        <v>0.05870056897584595</v>
       </c>
       <c r="AC3">
-        <v>-0.05996605274369608</v>
+        <v>0.2450458603372891</v>
       </c>
       <c r="AD3">
-        <v>172.4</v>
+        <v>13.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>172.4</v>
+        <v>13.6</v>
       </c>
       <c r="AG3">
-        <v>172.394</v>
+        <v>-4.9</v>
       </c>
       <c r="AH3">
-        <v>0.5029171528588098</v>
+        <v>0.02830974188176519</v>
       </c>
       <c r="AI3">
-        <v>0.6800788954635109</v>
+        <v>0.1728081321473952</v>
       </c>
       <c r="AJ3">
-        <v>0.5029084523066332</v>
+        <v>-0.01060835678718337</v>
       </c>
       <c r="AK3">
-        <v>0.6800713231871366</v>
+        <v>-0.08139534883720931</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="AN3">
+        <v>0.6868686868686869</v>
+      </c>
+      <c r="AO3">
+        <v>3.785046728971962</v>
+      </c>
+      <c r="AP3">
+        <v>-0.2474747474747475</v>
+      </c>
+      <c r="AQ3">
+        <v>3.785046728971962</v>
       </c>
     </row>
     <row r="4">
@@ -823,117 +847,239 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Salafin S.A. (CBSE:SLF)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0296</v>
+      </c>
+      <c r="E4">
+        <v>-0.109</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>7.8</v>
+      </c>
+      <c r="L4">
+        <v>0.109704641350211</v>
+      </c>
+      <c r="M4">
+        <v>0.489</v>
+      </c>
+      <c r="N4">
+        <v>0.002970838396111786</v>
+      </c>
+      <c r="O4">
+        <v>0.06269230769230769</v>
+      </c>
+      <c r="P4">
+        <v>0.489</v>
+      </c>
+      <c r="Q4">
+        <v>0.002970838396111786</v>
+      </c>
+      <c r="R4">
+        <v>0.06269230769230769</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="V4">
+        <v>5.467800729040097e-05</v>
+      </c>
+      <c r="W4">
+        <v>0.09617755856966709</v>
+      </c>
+      <c r="X4">
+        <v>0.0729643085293651</v>
+      </c>
+      <c r="Y4">
+        <v>0.02321325004030199</v>
+      </c>
+      <c r="Z4">
+        <v>0.2804800113612156</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06067503148531356</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06067503148531356</v>
+      </c>
+      <c r="AD4">
+        <v>175.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>175.9</v>
+      </c>
+      <c r="AG4">
+        <v>175.891</v>
+      </c>
+      <c r="AH4">
+        <v>0.5165932452276065</v>
+      </c>
+      <c r="AI4">
+        <v>0.6823118696664081</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5165804676188211</v>
+      </c>
+      <c r="AK4">
+        <v>0.6823007785376525</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Maroc Leasing S.A. (CBSE:MLE)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0242</v>
-      </c>
-      <c r="E4">
-        <v>-0.0574</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>3.86</v>
-      </c>
-      <c r="L4">
-        <v>0.01038192576654115</v>
-      </c>
-      <c r="M4">
-        <v>3.7252</v>
-      </c>
-      <c r="N4">
-        <v>0.03975667022411953</v>
-      </c>
-      <c r="O4">
-        <v>0.9650777202072539</v>
-      </c>
-      <c r="P4">
-        <v>3.7252</v>
-      </c>
-      <c r="Q4">
-        <v>0.03975667022411953</v>
-      </c>
-      <c r="R4">
-        <v>0.9650777202072539</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0.04004149377593361</v>
-      </c>
-      <c r="X4">
-        <v>0.1790210448888163</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1389795511128827</v>
-      </c>
-      <c r="Z4">
-        <v>0.3434642032332564</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07137856988360544</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07137856988360544</v>
-      </c>
-      <c r="AD4">
-        <v>1042.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1042.9</v>
-      </c>
-      <c r="AG4">
-        <v>1042.9</v>
-      </c>
-      <c r="AH4">
-        <v>0.9175611472813654</v>
-      </c>
-      <c r="AI4">
-        <v>0.9086077713887436</v>
-      </c>
-      <c r="AJ4">
-        <v>0.9175611472813654</v>
-      </c>
-      <c r="AK4">
-        <v>0.9086077713887436</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.0264</v>
+      </c>
+      <c r="E5">
+        <v>0.0433</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>8.74</v>
+      </c>
+      <c r="L5">
+        <v>0.02590397154712508</v>
+      </c>
+      <c r="M5">
+        <v>3.9198</v>
+      </c>
+      <c r="N5">
+        <v>0.03869496544916091</v>
+      </c>
+      <c r="O5">
+        <v>0.4484897025171624</v>
+      </c>
+      <c r="P5">
+        <v>3.9198</v>
+      </c>
+      <c r="Q5">
+        <v>0.03869496544916091</v>
+      </c>
+      <c r="R5">
+        <v>0.4484897025171624</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.08331744518589132</v>
+      </c>
+      <c r="X5">
+        <v>0.1929190186336958</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1096015734478045</v>
+      </c>
+      <c r="Z5">
+        <v>0.2939536504617529</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06750368417410149</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06750368417410149</v>
+      </c>
+      <c r="AD5">
+        <v>1011.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1011.4</v>
+      </c>
+      <c r="AG5">
+        <v>1011.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.9089601869326862</v>
+      </c>
+      <c r="AI5">
+        <v>0.9063536159154045</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9089601869326862</v>
+      </c>
+      <c r="AK5">
+        <v>0.9063536159154045</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
